--- a/program/산출물양식/[기획] WBS_A-COPilot.xlsx
+++ b/program/산출물양식/[기획] WBS_A-COPilot.xlsx
@@ -16,7 +16,7 @@
     <numFmt numFmtId="164" formatCode="mm/dd"/>
     <numFmt numFmtId="165" formatCode="m/d"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -40,6 +40,11 @@
       <name val="맑은 고딕"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -55,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -92,6 +97,21 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -370,6 +390,9 @@
   </sheetPr>
   <dimension ref="A1:Z249"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col width="62" customWidth="1" style="7" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" s="7">
       <c r="A1" s="1" t="inlineStr">
@@ -412,7 +435,11 @@
           <t>우선순위</t>
         </is>
       </c>
-      <c r="I1" s="1" t="n"/>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>진척 근거</t>
+        </is>
+      </c>
       <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
@@ -452,9 +479,9 @@
           <t>전체</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>진행중</t>
         </is>
       </c>
       <c r="F2" s="10" t="inlineStr">
@@ -472,7 +499,11 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="I2" s="4" t="n"/>
+      <c r="I2" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-02 점검 중. 담당별 WBS 분리본 작성(코어1)</t>
+        </is>
+      </c>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
@@ -512,9 +543,9 @@
           <t>전체</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>진행중</t>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
@@ -532,7 +563,11 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="I3" s="4" t="n"/>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>근거 41건 링크·근거출처 표·페인포인트 절 반영, 제목 계층 적용(2026-09-02)</t>
+        </is>
+      </c>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="1" t="n"/>
       <c r="L3" s="1" t="n"/>
@@ -632,9 +667,9 @@
           <t>전체</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>진행중</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
@@ -652,7 +687,11 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="I5" s="4" t="n"/>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>수집 완료 — 쿠팡 주문·배송 457건(송채영, 08-26~08-28), 소비자24 상담 1,704건·반품환불 사유 322건 동결(서유현, 08-17~08-27). 보고서 작성 남음</t>
+        </is>
+      </c>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="1" t="n"/>
       <c r="L5" s="1" t="n"/>
@@ -692,9 +731,9 @@
           <t>전체</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>진행중</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
@@ -712,7 +751,11 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="I6" s="4" t="n"/>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>코어 1 소유 테이블 6종 확정(customer_cases·case_events·shared_state·agent_runs·team_tasks·outbox)</t>
+        </is>
+      </c>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="1" t="n"/>
       <c r="L6" s="1" t="n"/>
@@ -1012,7 +1055,11 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="I11" s="4" t="n"/>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>재료 확보 — 법령·고시 조항 ID 앵커 28개, policy_rag 적재(서유현, 08-28)</t>
+        </is>
+      </c>
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="1" t="n"/>
       <c r="L11" s="1" t="n"/>
@@ -1052,9 +1099,9 @@
           <t>전체</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>진행중</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
@@ -1072,7 +1119,11 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="I12" s="4" t="n"/>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>Procurement + Order &amp; Payment 통합 모듈 설계 진행(김지혜, 08-28~09-02). ★v8 §8-B 는 이 둘을 통합 Team 하나로 규정한다 — 별도 모듈로 나누지 않는다</t>
+        </is>
+      </c>
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="1" t="n"/>
       <c r="L12" s="1" t="n"/>
@@ -1873,8 +1924,16 @@
     </row>
     <row r="29" ht="15.75" customHeight="1" s="7">
       <c r="A29" s="2" t="n"/>
-      <c r="B29" s="1" t="n"/>
-      <c r="C29" s="1" t="n"/>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>WBS 에 넣지 않은 보고</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>WBS 는 산출물 단위다. 개인 작업 단위 보고는 행이 되지 않고 해당 산출물의 진척 근거로 들어간다.</t>
+        </is>
+      </c>
       <c r="D29" s="1" t="n"/>
       <c r="E29" s="1" t="n"/>
       <c r="F29" s="6" t="n"/>
@@ -1901,8 +1960,16 @@
     </row>
     <row r="30" ht="15.75" customHeight="1" s="7">
       <c r="A30" s="2" t="n"/>
-      <c r="B30" s="1" t="n"/>
-      <c r="C30" s="1" t="n"/>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>코드 분석 · 담당 부분 코드 리뷰 (정세환)</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>상시 활동이라 산출물이 아니다. 마감이 비어 있어 WBS 에 넣으면 영원히 진행중으로 남는다. 리뷰 결과가 결함 리포트나 산출물 변경으로 이어질 때 그 산출물 행에 반영한다.</t>
+        </is>
+      </c>
       <c r="D30" s="1" t="n"/>
       <c r="E30" s="1" t="n"/>
       <c r="F30" s="6" t="n"/>
@@ -1957,8 +2024,16 @@
     </row>
     <row r="32" ht="15.75" customHeight="1" s="7">
       <c r="A32" s="2" t="n"/>
-      <c r="B32" s="1" t="n"/>
-      <c r="C32" s="1" t="n"/>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>Order&amp;Payment 기획 초안 / 모듈 구체화, Procurement 기획 초안 / 기획 구체화 (김지혜, 4행)</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>하루짜리 단위라 WBS 최말단(work package)보다 작다. 네 행을 011 의 진척 근거 한 줄로 접었다. ★그리고 v8 §8-B 는 Procurement 와 Order &amp; Payment 를 통합 Team 하나로 본다. 둘로 나눈 것 자체가 계획서와 어긋난다.</t>
+        </is>
+      </c>
       <c r="D32" s="1" t="n"/>
       <c r="E32" s="1" t="n"/>
       <c r="F32" s="6" t="n"/>
@@ -2013,8 +2088,16 @@
     </row>
     <row r="34" ht="15.75" customHeight="1" s="7">
       <c r="A34" s="2" t="n"/>
-      <c r="B34" s="1" t="n"/>
-      <c r="C34" s="1" t="n"/>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>서유현 개인 작업 48건</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>산출물이 아니라 개인 작업 로그다. 그중 산출물에 닿는 것만 004·010 의 진척 근거로 넣었다. 나머지는 TeamFlow 티켓으로 가는 것이 맞다(루트 CLAUDE.md — 스프린트·에픽은 TeamFlow 에서 관리).</t>
+        </is>
+      </c>
       <c r="D34" s="1" t="n"/>
       <c r="E34" s="1" t="n"/>
       <c r="F34" s="6" t="n"/>
